--- a/Assets/GameResource/Excel/词条效果说明表.xlsx
+++ b/Assets/GameResource/Excel/词条效果说明表.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UnityProject\LastGame\Assets\GameResource\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95420E5A-4C5E-4D06-B88F-21B3C52DC9A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA55CEC7-9285-46D4-820C-EC034590BE6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,68 +47,17 @@
     <t>词条名</t>
   </si>
   <si>
-    <t>御剑者移动N格</t>
-  </si>
-  <si>
-    <t>对飞剑与御剑者之间区域的敌人造成2点伤害</t>
-  </si>
-  <si>
-    <t>引爆【飞剑】，对剑格及邻格敌人造成4点伤害，并移除【飞剑】</t>
-  </si>
-  <si>
-    <t>一把不占格的飞剑，途径敌人时会造成4点伤害。</t>
-  </si>
-  <si>
     <t>虚弱</t>
   </si>
   <si>
-    <t>造成的伤害降低25%</t>
-  </si>
-  <si>
-    <t>受到的伤害提升25%</t>
-  </si>
-  <si>
-    <t>途径敌人时，获得1点能量。</t>
-  </si>
-  <si>
-    <t>途径敌人时，获得3点格挡。</t>
-  </si>
-  <si>
-    <t>飞剑·灵的残留印记，一个敌人只能残留一个灵剑。灵剑会在召剑后飞向御剑者并造成效果。</t>
-  </si>
-  <si>
     <t>灵剑</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>途径敌人时，会留下一道【灵剑】，召剑时会额外造成2点伤害。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>途径敌人时，会施加1层【虚弱】或者1层【易伤】。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>召剑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>移剑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>移形</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>链接</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>破剑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>飞剑</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -117,45 +66,103 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>附着：咒</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>附着：雷</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>附着：盾</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>易伤</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>无剑:指定格生成【飞剑】/有剑:【飞剑】会回到角色身边。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>【飞剑】移动数格</t>
+    <t>Id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Desc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>途经敌人时会造成4点伤害的剑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对敌人造成的伤害降低25%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自身受到的伤害提升25%</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>描述文本，要在配置层避免自引用或者循环引用
-用【】引用描述文本中出现的其他词条，用/区分双态文本
-条件1：文本1/条件2：文本2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Name</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Desc</t>
+用【】引用描述文本中出现的其他词条</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>御剑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>遁形</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>剑来</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>易位</t>
+  </si>
+  <si>
+    <t>御剑者与敌人发生位置的交换，但敌人间相对位置保持不变</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>御剑者召回【飞剑】和【灵剑】，摧毁每道回归的【灵剑】</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>移动【飞剑】至任意位置，对途经的敌人造成4点伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>飞剑获得灵力，途经敌人时可诞生一道【灵剑】，持续1回合消失</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>旋剑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>飞剑·灵途经敌人残留的印记，【剑来】或【链接】时摧毁灵剑并产生效果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>链接【飞剑】，每把【飞剑】/【灵剑】会给御剑者施加8点护甲。链接会摧毁【灵剑】，链接区域穿透所有敌人可能会产生额外效果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>旋转飞剑，会在回合结束时对剑格敌人造成3点伤害。处于旋剑状态后续旋剑使伤害叠加，御剑会使得旋剑停止</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>御剑者移动数格，移动至敌人格子时发生【易位】</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>消耗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本场战斗移除当前卡牌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>护甲</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>抵挡伤害的数量，下回合开始消失</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -494,19 +501,19 @@
   <dimension ref="A1:C16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.33203125" customWidth="1"/>
+    <col min="2" max="2" width="9.77734375" customWidth="1"/>
     <col min="3" max="3" width="63.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -528,7 +535,7 @@
         <v>3</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -536,10 +543,10 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -547,32 +554,32 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>3</v>
       </c>
-      <c r="B6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" t="s">
-        <v>4</v>
+      <c r="B6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>4</v>
       </c>
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" t="s">
-        <v>5</v>
+      <c r="B7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -580,98 +587,98 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" t="s">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" t="s">
-        <v>15</v>
+        <v>7</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" t="s">
-        <v>16</v>
+        <v>20</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>10</v>
-      </c>
-      <c r="B12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" t="s">
         <v>9</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="C13" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>12</v>
-      </c>
-      <c r="B14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C14" t="s">
-        <v>11</v>
+      <c r="C14" s="2" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B15" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="C15" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>14</v>
-      </c>
-      <c r="C16" t="s">
-        <v>13</v>
+        <v>8</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/GameResource/Excel/词条效果说明表.xlsx
+++ b/Assets/GameResource/Excel/词条效果说明表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UnityProject\LastGame\Assets\GameResource\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA55CEC7-9285-46D4-820C-EC034590BE6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{628232EE-0AFA-4049-AADD-8EF6D847086E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -118,10 +118,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>御剑者召回【飞剑】和【灵剑】，摧毁每道回归的【灵剑】</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>移动【飞剑】至任意位置，对途经的敌人造成4点伤害</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -134,14 +130,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>飞剑·灵途经敌人残留的印记，【剑来】或【链接】时摧毁灵剑并产生效果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>链接【飞剑】，每把【飞剑】/【灵剑】会给御剑者施加8点护甲。链接会摧毁【灵剑】，链接区域穿透所有敌人可能会产生额外效果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>旋转飞剑，会在回合结束时对剑格敌人造成3点伤害。处于旋剑状态后续旋剑使伤害叠加，御剑会使得旋剑停止</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -163,6 +151,18 @@
   </si>
   <si>
     <t>抵挡伤害的数量，下回合开始消失</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>御剑者召回【飞剑】和【灵剑】并造成途经伤害，摧毁每道回归的【灵剑】</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>飞剑·灵途经敌人残留的印记，对途经的敌人造成7点伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>链接所有【飞剑】/【灵剑】，每把获得8点护甲。链接区域穿透所有敌人可能会产生额外效果</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -565,10 +565,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -576,10 +576,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -601,7 +601,7 @@
         <v>17</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -612,7 +612,7 @@
         <v>18</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -634,7 +634,7 @@
         <v>19</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -645,7 +645,7 @@
         <v>6</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -653,10 +653,10 @@
         <v>11</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -667,7 +667,7 @@
         <v>5</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -678,7 +678,7 @@
         <v>8</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/GameResource/Excel/词条效果说明表.xlsx
+++ b/Assets/GameResource/Excel/词条效果说明表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UnityProject\LastGame\Assets\GameResource\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{628232EE-0AFA-4049-AADD-8EF6D847086E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73A8EA07-5A2E-44EE-93B6-71BD5E2A98D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -62,10 +62,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>附着：灵</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>易伤</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -111,58 +107,63 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>御剑者与敌人发生位置的交换，但敌人间相对位置保持不变</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>飞剑获得灵力，途经敌人时可诞生一道【灵剑】，持续1回合消失</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>旋剑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>旋转飞剑，会在回合结束时对剑格敌人造成3点伤害。处于旋剑状态后续旋剑使伤害叠加，御剑会使得旋剑停止</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>御剑者移动数格，移动至敌人格子时发生【易位】</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>消耗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本场战斗移除当前卡牌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>护甲</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>抵挡伤害的数量，下回合开始消失</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>御剑者召回【飞剑】和【灵剑】并造成途经伤害，摧毁每道回归的【灵剑】</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>飞剑·灵途经敌人残留的印记，对途经的敌人造成7点伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>链接所有【飞剑】/【灵剑】，每把获得8点护甲。链接区域穿透所有敌人可能会产生额外效果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>移动【飞剑】至任意位置，对途经的敌人造成5点伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>易位</t>
-  </si>
-  <si>
-    <t>御剑者与敌人发生位置的交换，但敌人间相对位置保持不变</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>移动【飞剑】至任意位置，对途经的敌人造成4点伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>飞剑获得灵力，途经敌人时可诞生一道【灵剑】，持续1回合消失</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>旋剑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>旋转飞剑，会在回合结束时对剑格敌人造成3点伤害。处于旋剑状态后续旋剑使伤害叠加，御剑会使得旋剑停止</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>御剑者移动数格，移动至敌人格子时发生【易位】</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>消耗</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>本场战斗移除当前卡牌</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>护甲</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>抵挡伤害的数量，下回合开始消失</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>御剑者召回【飞剑】和【灵剑】并造成途经伤害，摧毁每道回归的【灵剑】</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>飞剑·灵途经敌人残留的印记，对途经的敌人造成7点伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>链接所有【飞剑】/【灵剑】，每把获得8点护甲。链接区域穿透所有敌人可能会产生额外效果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>附着·灵</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -507,13 +508,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -535,7 +536,7 @@
         <v>3</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -546,7 +547,7 @@
         <v>4</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -554,10 +555,10 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -565,10 +566,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -576,10 +577,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -590,7 +591,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -598,10 +599,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -609,21 +610,21 @@
         <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>8</v>
       </c>
-      <c r="B11" t="s">
-        <v>20</v>
+      <c r="B11" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -631,10 +632,10 @@
         <v>9</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -645,7 +646,7 @@
         <v>6</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -653,32 +654,32 @@
         <v>11</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>12</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>13</v>
       </c>
-      <c r="B16" t="s">
-        <v>8</v>
+      <c r="B16" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/GameResource/Excel/词条效果说明表.xlsx
+++ b/Assets/GameResource/Excel/词条效果说明表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UnityProject\LastGame\Assets\GameResource\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73A8EA07-5A2E-44EE-93B6-71BD5E2A98D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{356AF0CB-FDBF-436A-BFF8-32608B29D386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
   <si>
     <t>int</t>
   </si>
@@ -111,18 +111,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>飞剑获得灵力，途经敌人时可诞生一道【灵剑】，持续1回合消失</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>旋剑</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>旋转飞剑，会在回合结束时对剑格敌人造成3点伤害。处于旋剑状态后续旋剑使伤害叠加，御剑会使得旋剑停止</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>御剑者移动数格，移动至敌人格子时发生【易位】</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -147,10 +139,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>飞剑·灵途经敌人残留的印记，对途经的敌人造成7点伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>链接所有【飞剑】/【灵剑】，每把获得8点护甲。链接区域穿透所有敌人可能会产生额外效果</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -164,6 +152,26 @@
   </si>
   <si>
     <t>附着·灵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>穿透</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>与【飞剑】/【灵剑】的【链接】经过了所有敌人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>【飞剑】获得灵力，途经敌人时可诞生一道【灵剑】，持续1回合消失</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>旋转【飞剑】，会在回合结束时对剑格敌人造成3点伤害。处于旋剑状态后续旋剑使伤害叠加，【御剑】会使得旋剑停止</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>【飞剑】途经敌人残留的印记，对途经的敌人造成7点伤害</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -499,7 +507,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="9.77734375" customWidth="1"/>
@@ -566,10 +574,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -577,10 +585,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -602,7 +610,7 @@
         <v>16</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -613,7 +621,7 @@
         <v>17</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -621,7 +629,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>19</v>
@@ -635,7 +643,7 @@
         <v>18</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -646,7 +654,7 @@
         <v>6</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -654,10 +662,10 @@
         <v>11</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -668,7 +676,7 @@
         <v>5</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -676,10 +684,21 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>20</v>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>14</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/GameResource/Excel/词条效果说明表.xlsx
+++ b/Assets/GameResource/Excel/词条效果说明表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UnityProject\LastGame\Assets\GameResource\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{356AF0CB-FDBF-436A-BFF8-32608B29D386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4F5309E-BB1C-4297-8B56-DDAC06C85028}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -662,10 +662,10 @@
         <v>11</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -673,10 +673,10 @@
         <v>12</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -684,10 +684,10 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -695,10 +695,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
